--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -3236,7 +3236,7 @@
         <v>132934660</v>
       </c>
       <c r="B27" t="n">
-        <v>91902</v>
+        <v>92056</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -3236,7 +3236,7 @@
         <v>132934660</v>
       </c>
       <c r="B27" t="n">
-        <v>92056</v>
+        <v>92058</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -3236,7 +3236,7 @@
         <v>132934660</v>
       </c>
       <c r="B27" t="n">
-        <v>92058</v>
+        <v>92071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
